--- a/artfynd/A 45750-2021 artfynd.xlsx
+++ b/artfynd/A 45750-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45750-2021 artfynd.xlsx
+++ b/artfynd/A 45750-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>93074861</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345913.3558260034</v>
+        <v>345913</v>
       </c>
       <c r="R2" t="n">
-        <v>6593259.287877769</v>
+        <v>6593259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-05-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>93074863</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345913.3558260034</v>
+        <v>345913</v>
       </c>
       <c r="R3" t="n">
-        <v>6593259.287877769</v>
+        <v>6593259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,19 +856,9 @@
           <t>2021-05-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-05-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
